--- a/Excel/Lookup Functions Practice (VLOOKUP, HLOOKUP, XLOOKUP).xlsx
+++ b/Excel/Lookup Functions Practice (VLOOKUP, HLOOKUP, XLOOKUP).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PRIYANSHI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\priyanshi_DA_17\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44C114C1-EBE5-40B4-B7B6-24CAE70FD94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFFF823-12F2-4D5F-AB04-FAFC5CA41DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{2A0CB5EC-5B9D-4D1B-9AB0-0F909BEE2D6A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{2A0CB5EC-5B9D-4D1B-9AB0-0F909BEE2D6A}"/>
   </bookViews>
   <sheets>
     <sheet name="VLOOKUP" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="55">
   <si>
     <t>EmployeeID</t>
   </si>
@@ -167,38 +168,38 @@
     <t>Bonus %</t>
   </si>
   <si>
-    <t>Task7:Find the Bonus % for IT department.</t>
+    <t>Task 10:If department is invalid, display "No Bonus Data".</t>
+  </si>
+  <si>
+    <t>Account</t>
+  </si>
+  <si>
+    <t>XLOOKUP Tasks (11–15)</t>
+  </si>
+  <si>
+    <t>Task 7:Find the Bonus % for IT department</t>
   </si>
   <si>
     <t>Task 8:Find the Bonus % for Finance department.</t>
   </si>
   <si>
-    <t>Task 9:Calculate Bonus Amount for employee E104
-(Bonus Amount = Salary × Bonus %)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bonus Amount </t>
-  </si>
-  <si>
-    <t>Task 10: If department is invalid, display "No Bonus Data".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account </t>
-  </si>
-  <si>
-    <t>XLOOKUP Tasks (11–15)</t>
+    <t>Task 9: Calculate Bonus Amount for employee E104
+(Bonus Amount = Salary × Bonus %).</t>
   </si>
   <si>
     <t>Task 11: Find Salary using EmployeeID.</t>
   </si>
   <si>
-    <t>Task 12: Find Department using Employee Name.</t>
+    <t>Task 12:Find Department using Employee Name.</t>
   </si>
   <si>
     <t>Task 13: Fetch Location of employee Rohit Verma.</t>
   </si>
   <si>
-    <t>Task 14: If EmployeeID = E999, return "Employee Not Found".</t>
+    <t>Rohit VermA</t>
+  </si>
+  <si>
+    <t>Task 14:If EmployeeID = E999, return "Employee Not Found".</t>
   </si>
   <si>
     <t>Task 15:Find Bonus % using XLOOKUP from Department_Bonus (horizontal lookup).</t>
@@ -208,7 +209,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,34 +252,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <color rgb="FF1F2328"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF1F2328"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -350,9 +330,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
@@ -375,66 +355,51 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -456,9 +421,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -496,7 +461,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -602,7 +567,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -744,7 +709,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -752,30 +717,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9210C4A-D8B9-40A1-AF37-39F1704C0AA7}">
-  <dimension ref="E1:L51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="E1:R51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="21.6640625" customWidth="1"/>
-    <col min="7" max="7" width="19.88671875" customWidth="1"/>
-    <col min="8" max="8" width="21.6640625" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" customWidth="1"/>
+    <col min="8" max="8" width="21.7109375" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="18.5546875" customWidth="1"/>
-    <col min="11" max="11" width="27.33203125" customWidth="1"/>
+    <col min="10" max="10" width="18.5703125" customWidth="1"/>
+    <col min="11" max="11" width="27.28515625" customWidth="1"/>
+    <col min="13" max="13" width="16.5703125" customWidth="1"/>
+    <col min="17" max="17" width="16.5703125" customWidth="1"/>
+    <col min="18" max="18" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="5:12" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="F1" s="23" t="s">
+    <row r="1" spans="5:18" ht="33" x14ac:dyDescent="0.25">
+      <c r="F1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-    </row>
-    <row r="2" spans="5:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="5:12" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="5:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="5:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F3" s="1" t="s">
         <v>0</v>
       </c>
@@ -795,7 +763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="5:12" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="5:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F4" s="3" t="s">
         <v>6</v>
       </c>
@@ -815,7 +783,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="5" spans="5:12" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="5:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F5" s="5" t="s">
         <v>10</v>
       </c>
@@ -834,8 +802,26 @@
       <c r="K5" s="5">
         <v>2018</v>
       </c>
-    </row>
-    <row r="6" spans="5:12" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="5:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F6" s="3" t="s">
         <v>14</v>
       </c>
@@ -854,8 +840,26 @@
       <c r="K6" s="3">
         <v>2020</v>
       </c>
-    </row>
-    <row r="7" spans="5:12" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M6" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="N6" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="O6" s="11">
+        <v>0.08</v>
+      </c>
+      <c r="P6" s="11">
+        <v>0.12</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="R6" s="11">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="7" spans="5:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F7" s="5" t="s">
         <v>18</v>
       </c>
@@ -875,7 +879,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="8" spans="5:12" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="5:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F8" s="3" t="s">
         <v>22</v>
       </c>
@@ -895,7 +899,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="9" spans="5:12" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="5:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F9" s="5" t="s">
         <v>25</v>
       </c>
@@ -915,7 +919,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="5:12" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="5:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F10" s="3" t="s">
         <v>28</v>
       </c>
@@ -935,7 +939,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="11" spans="5:12" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="5:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F11" s="5" t="s">
         <v>31</v>
       </c>
@@ -955,18 +959,18 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="15" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E15" s="22" t="s">
+    <row r="15" spans="5:18" x14ac:dyDescent="0.25">
+      <c r="E15" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-    </row>
-    <row r="16" spans="5:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="5:10" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+    </row>
+    <row r="16" spans="5:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="5:10" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F17" s="7" t="s">
         <v>0</v>
       </c>
@@ -974,7 +978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="5:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:10" x14ac:dyDescent="0.25">
       <c r="F18" t="s">
         <v>6</v>
       </c>
@@ -983,18 +987,18 @@
         <v>Rahul Sharma</v>
       </c>
     </row>
-    <row r="20" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E20" s="22" t="s">
+    <row r="20" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E20" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-    </row>
-    <row r="21" spans="5:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="5:10" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+    </row>
+    <row r="21" spans="5:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="5:10" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F22" s="1" t="s">
         <v>0</v>
       </c>
@@ -1002,7 +1006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="5:10" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="5:10" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F23" s="2" t="s">
         <v>14</v>
       </c>
@@ -1011,18 +1015,18 @@
         <v>IT</v>
       </c>
     </row>
-    <row r="25" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E25" s="22" t="s">
+    <row r="25" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E25" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-    </row>
-    <row r="27" spans="5:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="5:10" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+    </row>
+    <row r="27" spans="5:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="5:10" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F28" s="2" t="s">
         <v>1</v>
       </c>
@@ -1030,7 +1034,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="5:10" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="5:10" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F29" s="6" t="s">
         <v>19</v>
       </c>
@@ -1039,18 +1043,18 @@
         <v>58000</v>
       </c>
     </row>
-    <row r="32" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E32" s="24" t="s">
+    <row r="32" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E32" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="25"/>
-    </row>
-    <row r="34" spans="5:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="35" spans="5:10" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+    </row>
+    <row r="34" spans="5:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="5:10" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F35" s="1" t="s">
         <v>0</v>
       </c>
@@ -1058,7 +1062,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="5:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="5:10" x14ac:dyDescent="0.25">
       <c r="F36" t="s">
         <v>28</v>
       </c>
@@ -1067,18 +1071,18 @@
         <v>Hyderabad</v>
       </c>
     </row>
-    <row r="39" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E39" s="22" t="s">
+    <row r="39" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E39" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="20"/>
-    </row>
-    <row r="40" spans="5:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="41" spans="5:10" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+    </row>
+    <row r="40" spans="5:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="5:10" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F41" s="1" t="s">
         <v>0</v>
       </c>
@@ -1086,7 +1090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="5:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="5:10" x14ac:dyDescent="0.25">
       <c r="F42" t="s">
         <v>40</v>
       </c>
@@ -1095,18 +1099,18 @@
         <v>Not Found</v>
       </c>
     </row>
-    <row r="46" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E46" s="22" t="s">
+    <row r="46" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E46" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
-      <c r="J46" s="20"/>
-    </row>
-    <row r="48" spans="5:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="49" spans="6:7" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
+    </row>
+    <row r="48" spans="5:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="49" spans="6:7" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F49" s="1" t="s">
         <v>0</v>
       </c>
@@ -1114,7 +1118,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F51" t="s">
         <v>6</v>
       </c>
@@ -1140,755 +1144,286 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98088EA8-731A-4360-B232-791C16A58515}">
-  <dimension ref="E2:N44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="D2:N25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="22.33203125" customWidth="1"/>
-    <col min="6" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="10.21875" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" customWidth="1"/>
-    <col min="10" max="10" width="14.109375" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="12.28515625" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="5:14" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="E2" s="19" t="s">
+    <row r="2" spans="4:14" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="E2" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-    </row>
-    <row r="4" spans="5:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="5:14" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E5" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+    </row>
+    <row r="5" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D5" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="4:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="4:14" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="19">
+        <f>HLOOKUP(D8,VLOOKUP!P5:P6,2,0)</f>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="11" spans="4:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D11" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+    </row>
+    <row r="12" spans="4:14" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D12" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="19">
+        <f>HLOOKUP(D13,VLOOKUP!M5:R6,2,0)</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="16" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D16" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+    </row>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+    </row>
+    <row r="23" spans="4:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D23" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+    </row>
+    <row r="24" spans="4:7" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D24" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="5:14" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E6" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="9">
-        <v>45000</v>
-      </c>
-      <c r="J6" s="9">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="7" spans="5:14" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E7" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="11">
-        <v>52000</v>
-      </c>
-      <c r="J7" s="11">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="8" spans="5:14" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E8" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="9">
-        <v>65000</v>
-      </c>
-      <c r="J8" s="9">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="9" spans="5:14" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="11">
-        <v>58000</v>
-      </c>
-      <c r="J9" s="11">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="10" spans="5:14" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E10" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="9">
-        <v>48000</v>
-      </c>
-      <c r="J10" s="9">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="11" spans="5:14" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E11" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" s="11">
-        <v>62000</v>
-      </c>
-      <c r="J11" s="11">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="12" spans="5:14" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E12" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="9">
-        <v>47000</v>
-      </c>
-      <c r="J12" s="9">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="13" spans="5:14" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E13" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="11">
-        <v>54000</v>
-      </c>
-      <c r="J13" s="11">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="16" spans="5:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="5:10" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E17" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="5:10" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E18" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="G18" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="H18" s="16">
-        <v>0.12</v>
-      </c>
-      <c r="I18" s="16">
-        <v>0.15</v>
-      </c>
-      <c r="J18" s="16">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="22" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E22" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-    </row>
-    <row r="23" spans="5:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="5:10" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E24" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F26" s="17">
-        <f>HLOOKUP(E26,H17:H18,2,0)</f>
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="29" spans="5:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E29" s="18" t="s">
+    </row>
+    <row r="25" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
         <v>44</v>
       </c>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-    </row>
-    <row r="30" spans="5:10" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E30" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F31" s="17">
-        <f>HLOOKUP(E31,E17:J18,2,0)</f>
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="34" spans="5:7" x14ac:dyDescent="0.3">
-      <c r="E34" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-    </row>
-    <row r="35" spans="5:7" x14ac:dyDescent="0.3">
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-    </row>
-    <row r="36" spans="5:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="37" spans="5:7" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E37" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="F37" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="38" spans="5:7" x14ac:dyDescent="0.3">
-      <c r="E38" t="s">
-        <v>18</v>
-      </c>
-      <c r="F38">
-        <f>58000*(HLOOKUP(G9,E17:J18,2,0))</f>
-        <v>8700</v>
-      </c>
-    </row>
-    <row r="41" spans="5:7" x14ac:dyDescent="0.3">
-      <c r="E41" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-    </row>
-    <row r="42" spans="5:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="5:7" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E43" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="5:7" x14ac:dyDescent="0.3">
-      <c r="E44" t="s">
-        <v>48</v>
-      </c>
-      <c r="F44" s="17" t="str">
-        <f>IFERROR(HLOOKUP(E44,E17:J18,2,0),"No Bouns Data")</f>
+      <c r="E25" t="str">
+        <f>IFERROR(HLOOKUP(D25,VLOOKUP!M5:R6,2,0),"No Bouns Data")</f>
         <v>No Bouns Data</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="D16:G17"/>
+    <mergeCell ref="D23:G23"/>
     <mergeCell ref="E2:N2"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="E34:G35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16ABDB86-9B3B-4B2A-B62C-D38109124C07}">
-  <dimension ref="D2:K47"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="D2:J27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="15.88671875" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" customWidth="1"/>
-    <col min="7" max="7" width="19.109375" customWidth="1"/>
-    <col min="9" max="9" width="20.109375" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:11" ht="21" x14ac:dyDescent="0.4">
-      <c r="F2" s="26" t="s">
+    <row r="2" spans="4:10" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="E2" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+    </row>
+    <row r="4" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-    </row>
-    <row r="3" spans="4:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="4:11" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+    </row>
+    <row r="5" spans="4:10" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <f>_xlfn.XLOOKUP(E6,VLOOKUP!F3:F11,VLOOKUP!J3:J11)</f>
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="9" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E9" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+    </row>
+    <row r="10" spans="4:10" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F10" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="7" t="s">
+    </row>
+    <row r="11" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="str">
+        <f>_xlfn.XLOOKUP(XLOOKUP!E11,VLOOKUP!G3:G11,VLOOKUP!H3:H11)</f>
+        <v>IT</v>
+      </c>
+    </row>
+    <row r="15" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D15" s="23"/>
+      <c r="E15" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+    </row>
+    <row r="16" spans="4:10" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="4:11" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D5" s="9" t="s">
+    </row>
+    <row r="17" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" t="str">
+        <f>_xlfn.XLOOKUP(E17,VLOOKUP!G3:G11,VLOOKUP!I3:I11)</f>
+        <v>Bangalore</v>
+      </c>
+    </row>
+    <row r="21" spans="5:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E21" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+    </row>
+    <row r="22" spans="5:9" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E22" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="9">
-        <v>45000</v>
-      </c>
-      <c r="I5" s="9">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="6" spans="4:11" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D6" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="11">
-        <v>52000</v>
-      </c>
-      <c r="I6" s="11">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="7" spans="4:11" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="9">
-        <v>65000</v>
-      </c>
-      <c r="I7" s="9">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="8" spans="4:11" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D8" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="11">
-        <v>58000</v>
-      </c>
-      <c r="I8" s="11">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="9" spans="4:11" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D9" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="9">
-        <v>48000</v>
-      </c>
-      <c r="I9" s="9">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="10" spans="4:11" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D10" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="11">
-        <v>62000</v>
-      </c>
-      <c r="I10" s="11">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="11" spans="4:11" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D11" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="9">
-        <v>47000</v>
-      </c>
-      <c r="I11" s="9">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="12" spans="4:11" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D12" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="11">
-        <v>54000</v>
-      </c>
-      <c r="I12" s="11">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="14" spans="4:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="4:11" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D15" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="4:11" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D16" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="F16" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="G16" s="16">
-        <v>0.12</v>
-      </c>
-      <c r="H16" s="16">
-        <v>0.15</v>
-      </c>
-      <c r="I16" s="16">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D19" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-    </row>
-    <row r="20" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="4:7" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D21" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D22" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" t="str">
-        <f>_xlfn.XLOOKUP(D22,D5:D12,E5:E12)</f>
-        <v>Pooja Mehta</v>
-      </c>
-    </row>
-    <row r="25" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D25" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-    </row>
-    <row r="26" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="4:7" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D27" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D28" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" t="str">
-        <f>_xlfn.XLOOKUP(D28,E5:E12,F5:F12)</f>
-        <v>IT</v>
-      </c>
-    </row>
-    <row r="31" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D31" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-    </row>
-    <row r="32" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="33" spans="4:7" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D33" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D34" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" t="str">
-        <f>_xlfn.XLOOKUP(D34,E5:E12,G5:G12)</f>
-        <v>Bangalore</v>
-      </c>
-    </row>
-    <row r="37" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D37" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-    </row>
-    <row r="38" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="4:7" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D39" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D40" t="s">
-        <v>40</v>
-      </c>
-      <c r="E40" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(D40,D5:D12,E5:E12),"Employee Not Founf")</f>
-        <v>Employee Not Founf</v>
-      </c>
-    </row>
-    <row r="43" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D43" s="29" t="s">
+      <c r="F23" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(E23,VLOOKUP!F3:F11,VLOOKUP!G3:G11),"Employee Not Found")</f>
+        <v>Rahul Sharma</v>
+      </c>
+    </row>
+    <row r="27" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E27" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-    </row>
-    <row r="44" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="45" spans="4:7" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D45" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="46" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D46" t="s">
-        <v>16</v>
-      </c>
-      <c r="E46" s="17">
-        <f>_xlfn.XLOOKUP(D46,D15:I15,D16:I16)</f>
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="47" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D47" s="28"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="F2:K2"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="D43:G43"/>
+    <mergeCell ref="E27:I27"/>
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="E9:I9"/>
+    <mergeCell ref="E15:I15"/>
+    <mergeCell ref="E21:I21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>